--- a/diseases/d162/2000-2004.xlsx
+++ b/diseases/d162/2000-2004.xlsx
@@ -40107,7 +40107,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -41534,7 +41534,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -42961,7 +42961,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -44388,7 +44388,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -45815,7 +45815,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -47242,7 +47242,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -48669,7 +48669,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -50096,7 +50096,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -51523,7 +51523,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -52950,7 +52950,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -54377,7 +54377,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -55804,7 +55804,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -57470,7 +57470,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -58897,7 +58897,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -60324,7 +60324,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -61751,7 +61751,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -63178,7 +63178,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -64605,7 +64605,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -66032,7 +66032,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -67459,7 +67459,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -68886,7 +68886,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -70313,7 +70313,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -71740,7 +71740,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -73167,7 +73167,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">

--- a/diseases/d162/2000-2004.xlsx
+++ b/diseases/d162/2000-2004.xlsx
@@ -40107,7 +40107,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -41534,7 +41534,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -42961,7 +42961,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -44388,7 +44388,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -45815,7 +45815,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -47242,7 +47242,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -48669,7 +48669,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -50096,7 +50096,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -51523,7 +51523,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -52950,7 +52950,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -54377,7 +54377,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -55804,7 +55804,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -57470,7 +57470,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -58897,7 +58897,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -60324,7 +60324,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -61751,7 +61751,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -63178,7 +63178,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -64605,7 +64605,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -66032,7 +66032,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -67459,7 +67459,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -68886,7 +68886,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -70313,7 +70313,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -71740,7 +71740,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -73167,7 +73167,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">

--- a/diseases/d162/2000-2004.xlsx
+++ b/diseases/d162/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>19</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.3670645356445262</v>
       </c>
@@ -1639,9 +1636,6 @@
       <c r="O6" t="n">
         <v>13</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.2894763973192704</v>
       </c>
@@ -2035,9 +2029,6 @@
       <c r="O8" t="n">
         <v>15</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.2897877912983102</v>
       </c>
@@ -2670,9 +2661,6 @@
       <c r="O11" t="n">
         <v>18</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.4008134732112975</v>
       </c>
@@ -3066,9 +3054,6 @@
       <c r="O13" t="n">
         <v>9</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.1738726747789861</v>
       </c>
@@ -3701,9 +3686,6 @@
       <c r="O16" t="n">
         <v>12</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.267208982140865</v>
       </c>
@@ -4097,9 +4079,6 @@
       <c r="O18" t="n">
         <v>13</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.2511494191252021</v>
       </c>
@@ -4732,9 +4711,6 @@
       <c r="O21" t="n">
         <v>11</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -5128,9 +5104,6 @@
       <c r="O23" t="n">
         <v>13</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.2511494191252021</v>
       </c>
@@ -5763,9 +5736,6 @@
       <c r="O26" t="n">
         <v>21</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.4676157187465137</v>
       </c>
@@ -6159,9 +6129,6 @@
       <c r="O28" t="n">
         <v>13</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.2511494191252021</v>
       </c>
@@ -6794,9 +6761,6 @@
       <c r="O31" t="n">
         <v>12</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.267208982140865</v>
       </c>
@@ -7190,9 +7154,6 @@
       <c r="O33" t="n">
         <v>14</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.2704686052117561</v>
       </c>
@@ -7825,9 +7786,6 @@
       <c r="O36" t="n">
         <v>8</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -8221,9 +8179,6 @@
       <c r="O38" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -8856,9 +8811,6 @@
       <c r="O41" t="n">
         <v>19</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.4230808883897029</v>
       </c>
@@ -9252,9 +9204,6 @@
       <c r="O43" t="n">
         <v>5</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -9887,9 +9836,6 @@
       <c r="O46" t="n">
         <v>16</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.3562786428544867</v>
       </c>
@@ -10283,9 +10229,6 @@
       <c r="O48" t="n">
         <v>11</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.2125110469520941</v>
       </c>
@@ -10918,9 +10861,6 @@
       <c r="O51" t="n">
         <v>12</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.267208982140865</v>
       </c>
@@ -11314,9 +11254,6 @@
       <c r="O53" t="n">
         <v>11</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.2125110469520941</v>
       </c>
@@ -11949,9 +11886,6 @@
       <c r="O56" t="n">
         <v>22</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.4898831339249192</v>
       </c>
@@ -12345,9 +12279,6 @@
       <c r="O58" t="n">
         <v>15</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.2897877912983102</v>
       </c>
@@ -12980,9 +12911,6 @@
       <c r="O61" t="n">
         <v>11</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -13376,9 +13304,6 @@
       <c r="O63" t="n">
         <v>17</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.3276810915095709</v>
       </c>
@@ -14250,9 +14175,6 @@
       <c r="O67" t="n">
         <v>18</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.3987897175173036</v>
       </c>
@@ -14646,9 +14568,6 @@
       <c r="O69" t="n">
         <v>16</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.3084057331854785</v>
       </c>
@@ -15281,9 +15200,6 @@
       <c r="O72" t="n">
         <v>10</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -15677,9 +15593,6 @@
       <c r="O74" t="n">
         <v>11</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.2120289415650165</v>
       </c>
@@ -16312,9 +16225,6 @@
       <c r="O77" t="n">
         <v>8</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1772398744521349</v>
       </c>
@@ -16708,9 +16618,6 @@
       <c r="O79" t="n">
         <v>8</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.1542028665927392</v>
       </c>
@@ -17343,9 +17250,6 @@
       <c r="O82" t="n">
         <v>13</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.2880147959847193</v>
       </c>
@@ -17739,9 +17643,6 @@
       <c r="O84" t="n">
         <v>11</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.2120289415650165</v>
       </c>
@@ -18374,9 +18275,6 @@
       <c r="O87" t="n">
         <v>16</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.3544797489042699</v>
       </c>
@@ -18770,9 +18668,6 @@
       <c r="O89" t="n">
         <v>10</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.1927535832409241</v>
       </c>
@@ -19405,9 +19300,6 @@
       <c r="O92" t="n">
         <v>13</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.2880147959847193</v>
       </c>
@@ -19801,9 +19693,6 @@
       <c r="O94" t="n">
         <v>6</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -20436,9 +20325,6 @@
       <c r="O97" t="n">
         <v>11</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.2437048273716855</v>
       </c>
@@ -20832,9 +20718,6 @@
       <c r="O99" t="n">
         <v>13</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.2505796582132013</v>
       </c>
@@ -21467,9 +21350,6 @@
       <c r="O102" t="n">
         <v>12</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -21863,9 +21743,6 @@
       <c r="O104" t="n">
         <v>6</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -22498,9 +22375,6 @@
       <c r="O107" t="n">
         <v>9</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.1993948587586518</v>
       </c>
@@ -22894,9 +22768,6 @@
       <c r="O109" t="n">
         <v>13</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.2505796582132013</v>
       </c>
@@ -23529,9 +23400,6 @@
       <c r="O112" t="n">
         <v>18</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.3987897175173036</v>
       </c>
@@ -23925,9 +23793,6 @@
       <c r="O114" t="n">
         <v>12</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.2313042998891088</v>
       </c>
@@ -24560,9 +24425,6 @@
       <c r="O117" t="n">
         <v>18</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.3987897175173036</v>
       </c>
@@ -24956,9 +24818,6 @@
       <c r="O119" t="n">
         <v>9</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.1734782249168317</v>
       </c>
@@ -25591,9 +25450,6 @@
       <c r="O122" t="n">
         <v>11</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.2437048273716855</v>
       </c>
@@ -25987,9 +25843,6 @@
       <c r="O124" t="n">
         <v>12</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.2307450025439637</v>
       </c>
@@ -26861,9 +26714,6 @@
       <c r="O128" t="n">
         <v>13</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -27257,9 +27107,6 @@
       <c r="O130" t="n">
         <v>13</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.2499737527559606</v>
       </c>
@@ -27892,9 +27739,6 @@
       <c r="O133" t="n">
         <v>16</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.3525771405729466</v>
       </c>
@@ -28288,9 +28132,6 @@
       <c r="O135" t="n">
         <v>9</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.1730587519079727</v>
       </c>
@@ -28923,9 +28764,6 @@
       <c r="O138" t="n">
         <v>12</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.26443285542971</v>
       </c>
@@ -29319,9 +29157,6 @@
       <c r="O140" t="n">
         <v>14</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.2692025029679576</v>
       </c>
@@ -29954,9 +29789,6 @@
       <c r="O143" t="n">
         <v>19</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.4186853544303741</v>
       </c>
@@ -30350,9 +30182,6 @@
       <c r="O145" t="n">
         <v>12</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.2307450025439637</v>
       </c>
@@ -30985,9 +30814,6 @@
       <c r="O148" t="n">
         <v>20</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.4407214257161833</v>
       </c>
@@ -31381,9 +31207,6 @@
       <c r="O150" t="n">
         <v>8</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.1538300016959758</v>
       </c>
@@ -32016,9 +31839,6 @@
       <c r="O153" t="n">
         <v>20</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.4407214257161833</v>
       </c>
@@ -32412,9 +32232,6 @@
       <c r="O155" t="n">
         <v>13</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.2499737527559606</v>
       </c>
@@ -33047,9 +32864,6 @@
       <c r="O158" t="n">
         <v>19</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.4186853544303741</v>
       </c>
@@ -33443,9 +33257,6 @@
       <c r="O160" t="n">
         <v>7</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -34078,9 +33889,6 @@
       <c r="O163" t="n">
         <v>14</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.3085049980013284</v>
       </c>
@@ -34474,9 +34282,6 @@
       <c r="O165" t="n">
         <v>7</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -35109,9 +34914,6 @@
       <c r="O168" t="n">
         <v>25</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.5509017821452291</v>
       </c>
@@ -35505,9 +35307,6 @@
       <c r="O170" t="n">
         <v>15</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.2884312531799545</v>
       </c>
@@ -36140,9 +35939,6 @@
       <c r="O173" t="n">
         <v>21</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.4627574970019925</v>
       </c>
@@ -36536,9 +36332,6 @@
       <c r="O175" t="n">
         <v>11</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.2115162523319667</v>
       </c>
@@ -37171,9 +36964,6 @@
       <c r="O178" t="n">
         <v>17</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.3746132118587558</v>
       </c>
@@ -37567,9 +37357,6 @@
       <c r="O180" t="n">
         <v>11</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.2115162523319667</v>
       </c>
@@ -38202,9 +37989,6 @@
       <c r="O183" t="n">
         <v>10</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.2203607128580917</v>
       </c>
@@ -38598,9 +38382,6 @@
       <c r="O185" t="n">
         <v>10</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.1918297779282576</v>
       </c>
@@ -39472,9 +39253,6 @@
       <c r="O189" t="n">
         <v>13</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.284796115556243</v>
       </c>
@@ -39868,9 +39646,6 @@
       <c r="O191" t="n">
         <v>86</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.3794543221821783</v>
       </c>
@@ -40117,7 +39892,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -40264,9 +40039,6 @@
       <c r="O193" t="n">
         <v>13</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.2493787113067349</v>
       </c>
@@ -40899,9 +40671,6 @@
       <c r="O196" t="n">
         <v>17</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.3724256895735485</v>
       </c>
@@ -41295,9 +41064,6 @@
       <c r="O198" t="n">
         <v>59</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.2603233140552153</v>
       </c>
@@ -41544,7 +41310,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -41691,9 +41457,6 @@
       <c r="O200" t="n">
         <v>9</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1726468001354318</v>
       </c>
@@ -42326,9 +42089,6 @@
       <c r="O203" t="n">
         <v>15</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.3286109025648957</v>
       </c>
@@ -42722,9 +42482,6 @@
       <c r="O205" t="n">
         <v>76</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.3353317265795994</v>
       </c>
@@ -42971,7 +42728,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -43118,9 +42875,6 @@
       <c r="O207" t="n">
         <v>13</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.2493787113067349</v>
       </c>
@@ -43753,9 +43507,6 @@
       <c r="O210" t="n">
         <v>17</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.3724256895735485</v>
       </c>
@@ -44149,9 +43900,6 @@
       <c r="O212" t="n">
         <v>83</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.3662175435014046</v>
       </c>
@@ -44398,7 +44146,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -44545,9 +44293,6 @@
       <c r="O214" t="n">
         <v>3</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -45180,9 +44925,6 @@
       <c r="O217" t="n">
         <v>12</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.2628887220519165</v>
       </c>
@@ -45576,9 +45318,6 @@
       <c r="O219" t="n">
         <v>64</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.2823846118565048</v>
       </c>
@@ -45825,7 +45564,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -45972,9 +45711,6 @@
       <c r="O221" t="n">
         <v>12</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.2301957335139091</v>
       </c>
@@ -46607,9 +46343,6 @@
       <c r="O224" t="n">
         <v>24</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.5257774441038331</v>
       </c>
@@ -47003,9 +46736,6 @@
       <c r="O226" t="n">
         <v>59</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.2603233140552153</v>
       </c>
@@ -47252,7 +46982,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -47399,9 +47129,6 @@
       <c r="O228" t="n">
         <v>15</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.2877446668923864</v>
       </c>
@@ -48034,9 +47761,6 @@
       <c r="O231" t="n">
         <v>27</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.5914996246168123</v>
       </c>
@@ -48430,9 +48154,6 @@
       <c r="O233" t="n">
         <v>100</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.4412259560257887</v>
       </c>
@@ -48679,7 +48400,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -48826,9 +48547,6 @@
       <c r="O235" t="n">
         <v>7</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.1342808445497803</v>
       </c>
@@ -49461,9 +49179,6 @@
       <c r="O238" t="n">
         <v>22</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.4819626570951804</v>
       </c>
@@ -49857,9 +49572,6 @@
       <c r="O240" t="n">
         <v>95</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.4191646582244993</v>
       </c>
@@ -50106,7 +49818,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -50253,9 +49965,6 @@
       <c r="O242" t="n">
         <v>20</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.3836595558565151</v>
       </c>
@@ -50888,9 +50597,6 @@
       <c r="O245" t="n">
         <v>27</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.5914996246168123</v>
       </c>
@@ -51284,9 +50990,6 @@
       <c r="O247" t="n">
         <v>107</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.4721117729475939</v>
       </c>
@@ -51533,7 +51236,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -51680,9 +51383,6 @@
       <c r="O249" t="n">
         <v>9</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0.1726468001354318</v>
       </c>
@@ -52315,9 +52015,6 @@
       <c r="O252" t="n">
         <v>22</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.4819626570951804</v>
       </c>
@@ -52711,9 +52408,6 @@
       <c r="O254" t="n">
         <v>77</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.3397439861398573</v>
       </c>
@@ -52960,7 +52654,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -53107,9 +52801,6 @@
       <c r="O256" t="n">
         <v>18</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.3452936002708636</v>
       </c>
@@ -53742,9 +53433,6 @@
       <c r="O259" t="n">
         <v>21</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.460055263590854</v>
       </c>
@@ -54138,9 +53826,6 @@
       <c r="O261" t="n">
         <v>108</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.4765240325078517</v>
       </c>
@@ -54387,7 +54072,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -54534,9 +54219,6 @@
       <c r="O263" t="n">
         <v>5</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -55169,9 +54851,6 @@
       <c r="O266" t="n">
         <v>21</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.460055263590854</v>
       </c>
@@ -55565,9 +55244,6 @@
       <c r="O268" t="n">
         <v>101</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.4456382155860466</v>
       </c>
@@ -55814,7 +55490,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -55961,9 +55637,6 @@
       <c r="O270" t="n">
         <v>12</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.2295267846281322</v>
       </c>
@@ -56835,9 +56508,6 @@
       <c r="O274" t="n">
         <v>22</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.4791209437375898</v>
       </c>
@@ -57231,9 +56901,6 @@
       <c r="O276" t="n">
         <v>61</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.2681857292570099</v>
       </c>
@@ -57480,7 +57147,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -57627,9 +57294,6 @@
       <c r="O278" t="n">
         <v>8</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.1530178564187548</v>
       </c>
@@ -58262,9 +57926,6 @@
       <c r="O281" t="n">
         <v>28</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.6097902920296598</v>
       </c>
@@ -58658,9 +58319,6 @@
       <c r="O283" t="n">
         <v>129</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.5671468700681029</v>
       </c>
@@ -58907,7 +58565,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -59054,9 +58712,6 @@
       <c r="O285" t="n">
         <v>15</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.2869084807851652</v>
       </c>
@@ -59689,9 +59344,6 @@
       <c r="O288" t="n">
         <v>20</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.4355644943068998</v>
       </c>
@@ -60085,9 +59737,6 @@
       <c r="O290" t="n">
         <v>116</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.5099925343248057</v>
       </c>
@@ -60334,7 +59983,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -60481,9 +60130,6 @@
       <c r="O292" t="n">
         <v>9</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.1721450884710991</v>
       </c>
@@ -61116,9 +60762,6 @@
       <c r="O295" t="n">
         <v>18</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.3920080448762099</v>
       </c>
@@ -61512,9 +61155,6 @@
       <c r="O297" t="n">
         <v>83</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.3649084512841282</v>
       </c>
@@ -61761,7 +61401,7 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN298" t="b">
@@ -61908,9 +61548,6 @@
       <c r="O299" t="n">
         <v>5</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.09563616026172174</v>
       </c>
@@ -62543,9 +62180,6 @@
       <c r="O302" t="n">
         <v>19</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.4137862695915548</v>
       </c>
@@ -62939,9 +62573,6 @@
       <c r="O304" t="n">
         <v>128</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0.562750382703234</v>
       </c>
@@ -63188,7 +62819,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -63335,9 +62966,6 @@
       <c r="O306" t="n">
         <v>10</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.1912723205234435</v>
       </c>
@@ -63970,9 +63598,6 @@
       <c r="O309" t="n">
         <v>35</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.7622378650370747</v>
       </c>
@@ -64366,9 +63991,6 @@
       <c r="O311" t="n">
         <v>113</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.4968030722301987</v>
       </c>
@@ -64615,7 +64237,7 @@
       </c>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN312" t="b">
@@ -64762,9 +64384,6 @@
       <c r="O313" t="n">
         <v>10</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.1912723205234435</v>
       </c>
@@ -65397,9 +65016,6 @@
       <c r="O316" t="n">
         <v>13</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0.2831169212994849</v>
       </c>
@@ -65793,9 +65409,6 @@
       <c r="O318" t="n">
         <v>121</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.5319749711491508</v>
       </c>
@@ -66042,7 +65655,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -66189,9 +65802,6 @@
       <c r="O320" t="n">
         <v>17</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.3251629448898539</v>
       </c>
@@ -66824,9 +66434,6 @@
       <c r="O323" t="n">
         <v>20</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.4355644943068998</v>
       </c>
@@ -67220,9 +66827,6 @@
       <c r="O325" t="n">
         <v>123</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0.5407679458788888</v>
       </c>
@@ -67469,7 +67073,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -67616,9 +67220,6 @@
       <c r="O327" t="n">
         <v>11</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.2103995525757878</v>
       </c>
@@ -68251,9 +67852,6 @@
       <c r="O330" t="n">
         <v>22</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.4791209437375898</v>
       </c>
@@ -68647,9 +68245,6 @@
       <c r="O332" t="n">
         <v>174</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0.7649888014872086</v>
       </c>
@@ -68896,7 +68491,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -69043,9 +68638,6 @@
       <c r="O334" t="n">
         <v>13</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.2486540166804765</v>
       </c>
@@ -69678,9 +69270,6 @@
       <c r="O337" t="n">
         <v>21</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0.4573427190222448</v>
       </c>
@@ -70074,9 +69663,6 @@
       <c r="O339" t="n">
         <v>223</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.9804166823657903</v>
       </c>
@@ -70323,7 +69909,7 @@
       </c>
       <c r="AM340" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN340" t="b">
@@ -70470,9 +70056,6 @@
       <c r="O341" t="n">
         <v>8</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.1530178564187548</v>
       </c>
@@ -71105,9 +70688,6 @@
       <c r="O344" t="n">
         <v>20</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.4355644943068998</v>
       </c>
@@ -71501,9 +71081,6 @@
       <c r="O346" t="n">
         <v>202</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0.888090447703541</v>
       </c>
@@ -71750,7 +71327,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -71897,9 +71474,6 @@
       <c r="O348" t="n">
         <v>11</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.2103995525757878</v>
       </c>
@@ -72532,9 +72106,6 @@
       <c r="O351" t="n">
         <v>13</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0.2831169212994849</v>
       </c>
@@ -72928,9 +72499,6 @@
       <c r="O353" t="n">
         <v>224</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.9848131697306594</v>
       </c>
@@ -73177,7 +72745,7 @@
       </c>
       <c r="AM354" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN354" t="b">

--- a/diseases/d162/2000-2004.xlsx
+++ b/diseases/d162/2000-2004.xlsx
@@ -39882,7 +39882,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -41300,7 +41300,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -42718,7 +42718,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -44136,7 +44136,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -45554,7 +45554,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -46972,7 +46972,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -48390,7 +48390,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -49808,7 +49808,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -51226,7 +51226,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -52644,7 +52644,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -54062,7 +54062,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -55480,7 +55480,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -57137,7 +57137,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -58555,7 +58555,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -59973,7 +59973,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -61391,7 +61391,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -62809,7 +62809,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -64227,7 +64227,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -65645,7 +65645,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -67063,7 +67063,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -68481,7 +68481,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -69899,7 +69899,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -71317,7 +71317,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -72735,7 +72735,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
